--- a/ASTquizApp/qBanks/VSAT.xlsx
+++ b/ASTquizApp/qBanks/VSAT.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B7B391-0290-44EC-A8A0-9F967CCD5D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$83</definedName>
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="304" count="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="304">
   <si>
     <t>A</t>
   </si>
@@ -962,41 +966,37 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="49" formatCode="@"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1040,29 +1040,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1085,17 +1077,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -1146,25 +1146,23 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1202,7 +1200,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1236,6 +1234,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1270,9 +1269,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1378,7 +1378,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1445,28 +1445,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P83"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O83"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" width="15.855469" style="0"/>
-    <col min="2" max="2" hidden="1" customWidth="1" width="15.0" style="0"/>
-    <col min="3" max="3" hidden="1" customWidth="1" bestFit="1" width="6.7109375" style="0"/>
-    <col min="4" max="4" hidden="1" customWidth="1" width="17.855469" style="0"/>
-    <col min="5" max="5" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" bestFit="1" width="135.85547" style="0"/>
-    <col min="9" max="9" customWidth="1" width="11.425781" style="0"/>
-    <col min="10" max="10" customWidth="1" bestFit="1" width="18.0" style="0"/>
-    <col min="11" max="11" customWidth="1" width="13.425781" style="0"/>
-    <col min="12" max="12" customWidth="1" width="12.285156" style="0"/>
-    <col min="13" max="13" customWidth="1" width="9.7109375" style="0"/>
-    <col min="14" max="14" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="15" max="15" hidden="1" customWidth="1" bestFit="1" width="18.710938" style="0"/>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="135.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="10" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" hidden="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="1" ht="18.75" customFormat="1">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="2" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A2" s="4" t="s">
         <v>280</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>279</v>
       </c>
       <c r="C2" s="6">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>24</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>165</v>
@@ -1554,13 +1554,13 @@
         <v>3</v>
       </c>
       <c r="N2" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="45">
       <c r="A3" s="4" t="s">
         <v>280</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>279</v>
       </c>
       <c r="C3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>24</v>
@@ -1577,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>165</v>
@@ -1601,13 +1601,13 @@
         <v>2</v>
       </c>
       <c r="N3" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A4" s="4" t="s">
         <v>280</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>279</v>
       </c>
       <c r="C4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>24</v>
@@ -1624,7 +1624,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>165</v>
@@ -1648,13 +1648,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A5" s="4" t="s">
         <v>280</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>279</v>
       </c>
       <c r="C5" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>24</v>
@@ -1671,7 +1671,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>165</v>
@@ -1695,13 +1695,13 @@
         <v>3</v>
       </c>
       <c r="N5" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A6" s="4" t="s">
         <v>280</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>279</v>
       </c>
       <c r="C6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>24</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>165</v>
@@ -1742,13 +1742,13 @@
         <v>3</v>
       </c>
       <c r="N6" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="45">
       <c r="A7" s="4" t="s">
         <v>280</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>279</v>
       </c>
       <c r="C7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>165</v>
@@ -1789,13 +1789,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A8" s="4" t="s">
         <v>280</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>279</v>
       </c>
       <c r="C8" s="6">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>24</v>
@@ -1812,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>165</v>
@@ -1836,13 +1836,13 @@
         <v>2</v>
       </c>
       <c r="N8" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A9" s="4" t="s">
         <v>280</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>279</v>
       </c>
       <c r="C9" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -1859,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>176</v>
@@ -1879,13 +1879,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="75">
       <c r="A10" s="4" t="s">
         <v>280</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>279</v>
       </c>
       <c r="C10" s="6">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>24</v>
@@ -1902,7 +1902,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>165</v>
@@ -1926,13 +1926,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A11" s="4" t="s">
         <v>280</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>279</v>
       </c>
       <c r="C11" s="6">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>24</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>176</v>
@@ -1969,13 +1969,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A12" s="4" t="s">
         <v>280</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>279</v>
       </c>
       <c r="C12" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>24</v>
@@ -1992,7 +1992,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>165</v>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="75">
       <c r="A13" s="4" t="s">
         <v>280</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>279</v>
       </c>
       <c r="C13" s="6">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>24</v>
@@ -2039,7 +2039,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>165</v>
@@ -2063,13 +2063,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A14" s="4" t="s">
         <v>280</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>279</v>
       </c>
       <c r="C14" s="6">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>24</v>
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>165</v>
@@ -2110,13 +2110,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A15" s="4" t="s">
         <v>280</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>279</v>
       </c>
       <c r="C15" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>165</v>
@@ -2157,13 +2157,13 @@
         <v>2</v>
       </c>
       <c r="N15" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A16" s="4" t="s">
         <v>280</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>279</v>
       </c>
       <c r="C16" s="6">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>24</v>
@@ -2180,7 +2180,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>165</v>
@@ -2204,13 +2204,13 @@
         <v>3</v>
       </c>
       <c r="N16" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="17" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A17" s="4" t="s">
         <v>280</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>279</v>
       </c>
       <c r="C17" s="6">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>24</v>
@@ -2227,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>176</v>
@@ -2247,13 +2247,13 @@
         <v>0</v>
       </c>
       <c r="N17" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="18" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A18" s="4" t="s">
         <v>280</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>279</v>
       </c>
       <c r="C18" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>24</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>165</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="N18" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="19" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A19" s="4" t="s">
         <v>280</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>279</v>
       </c>
       <c r="C19" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>24</v>
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>165</v>
@@ -2341,13 +2341,13 @@
         <v>3</v>
       </c>
       <c r="N19" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A20" s="4" t="s">
         <v>280</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>279</v>
       </c>
       <c r="C20" s="6">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>24</v>
@@ -2364,7 +2364,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>176</v>
@@ -2384,13 +2384,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="21" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A21" s="4" t="s">
         <v>280</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>279</v>
       </c>
       <c r="C21" s="6">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>24</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>165</v>
@@ -2431,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="22" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A22" s="4" t="s">
         <v>280</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>279</v>
       </c>
       <c r="C22" s="6">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>24</v>
@@ -2454,7 +2454,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>165</v>
@@ -2478,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="23" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A23" s="4" t="s">
         <v>280</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>279</v>
       </c>
       <c r="C23" s="6">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
@@ -2501,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>165</v>
@@ -2525,13 +2525,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="24" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A24" s="4" t="s">
         <v>280</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>279</v>
       </c>
       <c r="C24" s="6">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>24</v>
@@ -2548,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>165</v>
@@ -2572,13 +2572,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O24" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="25" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A25" s="4" t="s">
         <v>280</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>279</v>
       </c>
       <c r="C25" s="6">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>24</v>
@@ -2595,7 +2595,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>176</v>
@@ -2615,13 +2615,13 @@
         <v>3</v>
       </c>
       <c r="N25" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="26" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A26" s="4" t="s">
         <v>280</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>279</v>
       </c>
       <c r="C26" s="6">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>24</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>165</v>
@@ -2662,13 +2662,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="27" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A27" s="4" t="s">
         <v>280</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>279</v>
       </c>
       <c r="C27" s="6">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>24</v>
@@ -2685,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>165</v>
@@ -2709,13 +2709,13 @@
         <v>3</v>
       </c>
       <c r="N27" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="28" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A28" s="4" t="s">
         <v>280</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>279</v>
       </c>
       <c r="C28" s="6">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>24</v>
@@ -2732,7 +2732,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>176</v>
@@ -2752,13 +2752,13 @@
         <v>0</v>
       </c>
       <c r="N28" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="29" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A29" s="4" t="s">
         <v>280</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>279</v>
       </c>
       <c r="C29" s="6">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>24</v>
@@ -2775,7 +2775,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>165</v>
@@ -2799,13 +2799,13 @@
         <v>3</v>
       </c>
       <c r="N29" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="30" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A30" s="4" t="s">
         <v>280</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>279</v>
       </c>
       <c r="C30" s="6">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>24</v>
@@ -2822,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>176</v>
@@ -2842,13 +2842,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="31" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A31" s="4" t="s">
         <v>280</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>279</v>
       </c>
       <c r="C31" s="6">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>24</v>
@@ -2865,7 +2865,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>165</v>
@@ -2889,13 +2889,13 @@
         <v>3</v>
       </c>
       <c r="N31" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="32" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A32" s="4" t="s">
         <v>280</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>279</v>
       </c>
       <c r="C32" s="6">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>24</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>176</v>
@@ -2932,13 +2932,13 @@
         <v>0</v>
       </c>
       <c r="N32" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O32" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="33" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A33" s="4" t="s">
         <v>280</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>279</v>
       </c>
       <c r="C33" s="6">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>24</v>
@@ -2955,7 +2955,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>165</v>
@@ -2979,13 +2979,13 @@
         <v>0</v>
       </c>
       <c r="N33" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="34" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A34" s="4" t="s">
         <v>280</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>279</v>
       </c>
       <c r="C34" s="6">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>24</v>
@@ -3002,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>176</v>
@@ -3022,13 +3022,13 @@
         <v>0</v>
       </c>
       <c r="N34" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="35" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A35" s="4" t="s">
         <v>280</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>279</v>
       </c>
       <c r="C35" s="6">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>24</v>
@@ -3045,7 +3045,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>176</v>
@@ -3065,13 +3065,13 @@
         <v>3</v>
       </c>
       <c r="N35" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="36" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A36" s="4" t="s">
         <v>280</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>279</v>
       </c>
       <c r="C36" s="6">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>24</v>
@@ -3088,7 +3088,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>165</v>
@@ -3112,13 +3112,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="37" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A37" s="4" t="s">
         <v>280</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>279</v>
       </c>
       <c r="C37" s="6">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>24</v>
@@ -3135,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>176</v>
@@ -3155,13 +3155,13 @@
         <v>3</v>
       </c>
       <c r="N37" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="38" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="38" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A38" s="4" t="s">
         <v>280</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>279</v>
       </c>
       <c r="C38" s="6">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>24</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>165</v>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="N38" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="39" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="39" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A39" s="4" t="s">
         <v>280</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>279</v>
       </c>
       <c r="C39" s="6">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>24</v>
@@ -3225,7 +3225,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>165</v>
@@ -3249,13 +3249,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="40" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A40" s="4" t="s">
         <v>280</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>279</v>
       </c>
       <c r="C40" s="6">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>24</v>
@@ -3272,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>165</v>
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="N40" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O40" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="41" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A41" s="4" t="s">
         <v>280</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>279</v>
       </c>
       <c r="C41" s="6">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>24</v>
@@ -3319,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>165</v>
@@ -3343,13 +3343,13 @@
         <v>3</v>
       </c>
       <c r="N41" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="42" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A42" s="4" t="s">
         <v>280</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>279</v>
       </c>
       <c r="C42" s="6">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>24</v>
@@ -3366,7 +3366,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>165</v>
@@ -3390,13 +3390,13 @@
         <v>3</v>
       </c>
       <c r="N42" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="43" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A43" s="4" t="s">
         <v>280</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>279</v>
       </c>
       <c r="C43" s="6">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>24</v>
@@ -3413,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>176</v>
@@ -3433,13 +3433,13 @@
         <v>0</v>
       </c>
       <c r="N43" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="44" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A44" s="4" t="s">
         <v>280</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>279</v>
       </c>
       <c r="C44" s="6">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>24</v>
@@ -3456,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>176</v>
@@ -3476,13 +3476,13 @@
         <v>3</v>
       </c>
       <c r="N44" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O44" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="45" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A45" s="4" t="s">
         <v>280</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>279</v>
       </c>
       <c r="C45" s="6">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>24</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>176</v>
@@ -3519,13 +3519,13 @@
         <v>3</v>
       </c>
       <c r="N45" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="46" spans="8:8" s="3" ht="24.0" customFormat="1" customHeight="1">
+    <row r="46" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A46" s="4" t="s">
         <v>280</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>279</v>
       </c>
       <c r="C46" s="6">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
@@ -3542,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>176</v>
@@ -3562,13 +3562,13 @@
         <v>3</v>
       </c>
       <c r="N46" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O46" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="8:8" s="3" ht="90.0" customFormat="1">
+    <row r="47" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A47" s="4" t="s">
         <v>280</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>279</v>
       </c>
       <c r="C47" s="6">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>24</v>
@@ -3585,7 +3585,7 @@
         <v>3</v>
       </c>
       <c r="F47" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>176</v>
@@ -3605,13 +3605,13 @@
         <v>3</v>
       </c>
       <c r="N47" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O47" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="48" spans="8:8" s="3" ht="90.0" customFormat="1">
+    <row r="48" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A48" s="4" t="s">
         <v>280</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>279</v>
       </c>
       <c r="C48" s="6">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
@@ -3628,7 +3628,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>176</v>
@@ -3648,13 +3648,13 @@
         <v>0</v>
       </c>
       <c r="N48" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O48" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="8:8" s="3" ht="90.0" customFormat="1">
+    <row r="49" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A49" s="4" t="s">
         <v>280</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>279</v>
       </c>
       <c r="C49" s="6">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>24</v>
@@ -3671,7 +3671,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>176</v>
@@ -3691,13 +3691,13 @@
         <v>0</v>
       </c>
       <c r="N49" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O49" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="50" spans="8:8" s="3" ht="90.0" customFormat="1">
+    <row r="50" spans="1:15" s="3" customFormat="1" ht="30">
       <c r="A50" s="4" t="s">
         <v>280</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>279</v>
       </c>
       <c r="C50" s="6">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
@@ -3714,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>176</v>
@@ -3734,13 +3734,13 @@
         <v>3</v>
       </c>
       <c r="N50" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="51" spans="8:8" ht="24.0" customHeight="1">
+    <row r="51" spans="1:15" ht="30">
       <c r="A51" s="4" t="s">
         <v>280</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>279</v>
       </c>
       <c r="C51" s="6">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>176</v>
@@ -3777,13 +3777,13 @@
         <v>3</v>
       </c>
       <c r="N51" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="8:8" ht="75.75">
+    <row r="52" spans="1:15" ht="30">
       <c r="A52" s="4" t="s">
         <v>280</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>279</v>
       </c>
       <c r="C52" s="6">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>164</v>
@@ -3800,7 +3800,7 @@
         <v>3</v>
       </c>
       <c r="F52" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>165</v>
@@ -3824,13 +3824,13 @@
         <v>3</v>
       </c>
       <c r="N52" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="8:8" ht="75.75">
+    <row r="53" spans="1:15" ht="30">
       <c r="A53" s="4" t="s">
         <v>280</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>279</v>
       </c>
       <c r="C53" s="6">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>164</v>
@@ -3847,7 +3847,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>165</v>
@@ -3871,13 +3871,13 @@
         <v>2</v>
       </c>
       <c r="N53" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="8:8" ht="90.75">
+    <row r="54" spans="1:15" ht="30">
       <c r="A54" s="4" t="s">
         <v>280</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>279</v>
       </c>
       <c r="C54" s="6">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>164</v>
@@ -3894,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>176</v>
@@ -3914,13 +3914,13 @@
         <v>3</v>
       </c>
       <c r="N54" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="8:8" ht="75.75">
+    <row r="55" spans="1:15" ht="30">
       <c r="A55" s="4" t="s">
         <v>280</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>279</v>
       </c>
       <c r="C55" s="6">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>164</v>
@@ -3937,7 +3937,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>165</v>
@@ -3961,13 +3961,13 @@
         <v>3</v>
       </c>
       <c r="N55" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="8:8" ht="75.75">
+    <row r="56" spans="1:15" ht="75">
       <c r="A56" s="4" t="s">
         <v>280</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>279</v>
       </c>
       <c r="C56" s="6">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>164</v>
@@ -3984,7 +3984,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>165</v>
@@ -4008,13 +4008,13 @@
         <v>2</v>
       </c>
       <c r="N56" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="8:8" ht="75.75">
+    <row r="57" spans="1:15" ht="45">
       <c r="A57" s="4" t="s">
         <v>280</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>279</v>
       </c>
       <c r="C57" s="6">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>164</v>
@@ -4031,7 +4031,7 @@
         <v>3</v>
       </c>
       <c r="F57" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>165</v>
@@ -4055,13 +4055,13 @@
         <v>0</v>
       </c>
       <c r="N57" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="8:8" ht="75.75">
+    <row r="58" spans="1:15" ht="30">
       <c r="A58" s="4" t="s">
         <v>280</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>279</v>
       </c>
       <c r="C58" s="6">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>164</v>
@@ -4078,7 +4078,7 @@
         <v>3</v>
       </c>
       <c r="F58" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>165</v>
@@ -4102,13 +4102,13 @@
         <v>3</v>
       </c>
       <c r="N58" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O58" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="8:8" ht="75.75">
+    <row r="59" spans="1:15" ht="30">
       <c r="A59" s="4" t="s">
         <v>280</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>279</v>
       </c>
       <c r="C59" s="6">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>164</v>
@@ -4125,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>165</v>
@@ -4149,13 +4149,13 @@
         <v>3</v>
       </c>
       <c r="N59" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="60" spans="8:8" ht="75.75">
+    <row r="60" spans="1:15" ht="45">
       <c r="A60" s="4" t="s">
         <v>280</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>279</v>
       </c>
       <c r="C60" s="6">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>164</v>
@@ -4172,7 +4172,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>165</v>
@@ -4196,13 +4196,13 @@
         <v>3</v>
       </c>
       <c r="N60" s="9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O60" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="8:8" ht="90.75">
+    <row r="61" spans="1:15" ht="30">
       <c r="A61" s="4" t="s">
         <v>280</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>279</v>
       </c>
       <c r="C61" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>164</v>
@@ -4219,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>176</v>
@@ -4239,13 +4239,13 @@
         <v>0</v>
       </c>
       <c r="N61" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O61" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="8:8" ht="90.75">
+    <row r="62" spans="1:15" ht="30">
       <c r="A62" s="4" t="s">
         <v>280</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>279</v>
       </c>
       <c r="C62" s="6">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>164</v>
@@ -4262,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>176</v>
@@ -4282,13 +4282,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O62" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="63" spans="8:8" ht="75.0" customFormat="1">
+    <row r="63" spans="1:15" ht="30">
       <c r="A63" s="4" t="s">
         <v>280</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>279</v>
       </c>
       <c r="C63" s="6">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>204</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>165</v>
@@ -4329,13 +4329,13 @@
         <v>1</v>
       </c>
       <c r="N63" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O63" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="8:8" ht="75.0" customFormat="1">
+    <row r="64" spans="1:15" ht="30">
       <c r="A64" s="4" t="s">
         <v>280</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>279</v>
       </c>
       <c r="C64" s="6">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>204</v>
@@ -4352,7 +4352,7 @@
         <v>3</v>
       </c>
       <c r="F64" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>165</v>
@@ -4376,13 +4376,13 @@
         <v>0</v>
       </c>
       <c r="N64" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O64" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="65" spans="8:8" ht="75.0" customFormat="1">
+    <row r="65" spans="1:15" ht="30">
       <c r="A65" s="4" t="s">
         <v>280</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>279</v>
       </c>
       <c r="C65" s="6">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>204</v>
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>165</v>
@@ -4423,13 +4423,13 @@
         <v>3</v>
       </c>
       <c r="N65" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O65" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="8:8" ht="75.0" customFormat="1">
+    <row r="66" spans="1:15" ht="30">
       <c r="A66" s="4" t="s">
         <v>280</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>279</v>
       </c>
       <c r="C66" s="6">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>204</v>
@@ -4446,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>165</v>
@@ -4470,13 +4470,13 @@
         <v>2</v>
       </c>
       <c r="N66" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O66" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="8:8" ht="75.0" customFormat="1">
+    <row r="67" spans="1:15" ht="45">
       <c r="A67" s="4" t="s">
         <v>280</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>279</v>
       </c>
       <c r="C67" s="6">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>225</v>
@@ -4493,7 +4493,7 @@
         <v>3</v>
       </c>
       <c r="F67" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>165</v>
@@ -4517,13 +4517,13 @@
         <v>1</v>
       </c>
       <c r="N67" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O67" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="8:8" ht="75.0" customFormat="1">
+    <row r="68" spans="1:15" ht="45">
       <c r="A68" s="4" t="s">
         <v>280</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>279</v>
       </c>
       <c r="C68" s="6">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>225</v>
@@ -4540,7 +4540,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>165</v>
@@ -4564,13 +4564,13 @@
         <v>3</v>
       </c>
       <c r="N68" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O68" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="69" spans="8:8" ht="75.0" customFormat="1">
+    <row r="69" spans="1:15" ht="45">
       <c r="A69" s="4" t="s">
         <v>280</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>279</v>
       </c>
       <c r="C69" s="6">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>225</v>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>165</v>
@@ -4611,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="N69" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="70" spans="8:8" ht="75.0" customFormat="1">
+    <row r="70" spans="1:15" ht="45">
       <c r="A70" s="4" t="s">
         <v>280</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>279</v>
       </c>
       <c r="C70" s="6">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>225</v>
@@ -4634,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>165</v>
@@ -4658,13 +4658,13 @@
         <v>3</v>
       </c>
       <c r="N70" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O70" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="71" spans="8:8" ht="75.0" customFormat="1">
+    <row r="71" spans="1:15" ht="30">
       <c r="A71" s="4" t="s">
         <v>280</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>279</v>
       </c>
       <c r="C71" s="6">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>242</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="F71" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>165</v>
@@ -4705,13 +4705,13 @@
         <v>2</v>
       </c>
       <c r="N71" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O71" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="72" spans="8:8" ht="75.0" customFormat="1">
+    <row r="72" spans="1:15" ht="30">
       <c r="A72" s="4" t="s">
         <v>280</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>279</v>
       </c>
       <c r="C72" s="6">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>248</v>
@@ -4728,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>165</v>
@@ -4752,13 +4752,13 @@
         <v>3</v>
       </c>
       <c r="N72" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O72" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="8:8" ht="75.0" customFormat="1">
+    <row r="73" spans="1:15" ht="30">
       <c r="A73" s="4" t="s">
         <v>280</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>279</v>
       </c>
       <c r="C73" s="6">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>248</v>
@@ -4775,7 +4775,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>165</v>
@@ -4799,13 +4799,13 @@
         <v>0</v>
       </c>
       <c r="N73" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O73" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="74" spans="8:8" ht="75.0" customFormat="1">
+    <row r="74" spans="1:15" ht="30">
       <c r="A74" s="4" t="s">
         <v>280</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>279</v>
       </c>
       <c r="C74" s="6">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>248</v>
@@ -4822,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>165</v>
@@ -4846,13 +4846,13 @@
         <v>1</v>
       </c>
       <c r="N74" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O74" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="8:8" ht="75.0" customFormat="1">
+    <row r="75" spans="1:15" ht="30">
       <c r="A75" s="4" t="s">
         <v>280</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>279</v>
       </c>
       <c r="C75" s="6">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>261</v>
@@ -4869,7 +4869,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>165</v>
@@ -4893,13 +4893,13 @@
         <v>0</v>
       </c>
       <c r="N75" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O75" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="8:8" ht="75.0" customFormat="1">
+    <row r="76" spans="1:15" ht="45">
       <c r="A76" s="4" t="s">
         <v>280</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>279</v>
       </c>
       <c r="C76" s="6">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>261</v>
@@ -4916,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>165</v>
@@ -4940,13 +4940,13 @@
         <v>2</v>
       </c>
       <c r="N76" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O76" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="77" spans="8:8" ht="75.0" customFormat="1">
+    <row r="77" spans="1:15" ht="60">
       <c r="A77" s="4" t="s">
         <v>280</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>279</v>
       </c>
       <c r="C77" s="6">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>269</v>
@@ -4963,7 +4963,7 @@
         <v>3</v>
       </c>
       <c r="F77" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>165</v>
@@ -4987,13 +4987,13 @@
         <v>3</v>
       </c>
       <c r="N77" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O77" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="78" spans="8:8" ht="75.0" customFormat="1">
+    <row r="78" spans="1:15" ht="60">
       <c r="A78" s="4" t="s">
         <v>280</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>279</v>
       </c>
       <c r="C78" s="6">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>269</v>
@@ -5010,7 +5010,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>165</v>
@@ -5034,13 +5034,13 @@
         <v>2</v>
       </c>
       <c r="N78" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O78" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="79" spans="8:8" s="16" ht="60.0" customFormat="1">
+    <row r="79" spans="1:15" s="16" customFormat="1" ht="30">
       <c r="A79" s="17" t="s">
         <v>290</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>279</v>
       </c>
       <c r="C79" s="6">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>261</v>
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>165</v>
@@ -5081,13 +5081,13 @@
         <v>0</v>
       </c>
       <c r="N79" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O79" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="80" spans="8:8" s="16" ht="75.0" customFormat="1">
+    <row r="80" spans="1:15" s="16" customFormat="1" ht="30">
       <c r="A80" s="17" t="s">
         <v>290</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>279</v>
       </c>
       <c r="C80" s="6">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>291</v>
@@ -5104,7 +5104,7 @@
         <v>3</v>
       </c>
       <c r="F80" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>176</v>
@@ -5124,13 +5124,13 @@
         <v>3</v>
       </c>
       <c r="N80" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O80" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="81" spans="8:8" s="16" ht="75.0" customFormat="1">
+    <row r="81" spans="1:15" s="16" customFormat="1" ht="30">
       <c r="A81" s="17" t="s">
         <v>290</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>279</v>
       </c>
       <c r="C81" s="6">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>291</v>
@@ -5147,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>176</v>
@@ -5167,13 +5167,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O81" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="8:8" s="16" ht="60.0" customFormat="1">
+    <row r="82" spans="1:15" s="16" customFormat="1" ht="45">
       <c r="A82" s="17" t="s">
         <v>290</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>279</v>
       </c>
       <c r="C82" s="6">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>291</v>
@@ -5190,7 +5190,7 @@
         <v>3</v>
       </c>
       <c r="F82" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>165</v>
@@ -5214,13 +5214,13 @@
         <v>0</v>
       </c>
       <c r="N82" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O82" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="83" spans="8:8" s="16" ht="60.0" customFormat="1">
+    <row r="83" spans="1:15" s="16" customFormat="1" ht="45">
       <c r="A83" s="17" t="s">
         <v>290</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>279</v>
       </c>
       <c r="C83" s="6">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>291</v>
@@ -5237,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>165</v>
@@ -5261,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="N83" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O83" s="5" t="s">
         <v>203</v>
@@ -5269,38 +5269,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H56:H58 H60">
-    <cfRule type="duplicateValues" priority="3" dxfId="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="duplicateValues" priority="1" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H54" r:id="rId1" tooltip="Narrowband"/>
+    <hyperlink ref="H54" r:id="rId1" tooltip="Narrowband" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>